--- a/artfynd/A 18942-2026 artfynd.xlsx
+++ b/artfynd/A 18942-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118269048</v>
+        <v>118269044</v>
       </c>
       <c r="B2" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514213</v>
+        <v>514276</v>
       </c>
       <c r="R2" t="n">
-        <v>7001780</v>
+        <v>7001757</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118269046</v>
+        <v>118269049</v>
       </c>
       <c r="B3" t="n">
-        <v>79073</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514221</v>
+        <v>514224</v>
       </c>
       <c r="R3" t="n">
-        <v>7001779</v>
+        <v>7001797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118269049</v>
+        <v>118269052</v>
       </c>
       <c r="B4" t="n">
-        <v>91969</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514224</v>
+        <v>514249</v>
       </c>
       <c r="R4" t="n">
-        <v>7001797</v>
+        <v>7001726</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,40 +966,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118269050</v>
+        <v>118473279</v>
       </c>
       <c r="B5" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kroktjärnen, Jmt</t>
@@ -1024,10 +1007,10 @@
         <v>514276</v>
       </c>
       <c r="R5" t="n">
-        <v>7001786</v>
+        <v>7001757</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,6 +1048,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118269044</v>
+        <v>118269048</v>
       </c>
       <c r="B6" t="n">
-        <v>78129</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1102,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514276</v>
+        <v>514213</v>
       </c>
       <c r="R6" t="n">
-        <v>7001757</v>
+        <v>7001780</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,37 +1164,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118269043</v>
+        <v>118269050</v>
       </c>
       <c r="B7" t="n">
-        <v>79601</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514303</v>
+        <v>514276</v>
       </c>
       <c r="R7" t="n">
-        <v>7001744</v>
+        <v>7001786</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,15 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118269045</v>
+        <v>118269042</v>
       </c>
       <c r="B8" t="n">
-        <v>77416</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1296,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514224</v>
+        <v>514341</v>
       </c>
       <c r="R8" t="n">
-        <v>7001774</v>
+        <v>7001752</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,37 +1358,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118269047</v>
+        <v>118269041</v>
       </c>
       <c r="B9" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,13 +1393,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514219</v>
+        <v>514340</v>
       </c>
       <c r="R9" t="n">
-        <v>7001782</v>
+        <v>7001752</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,15 +1455,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118473279</v>
+        <v>118269043</v>
       </c>
       <c r="B10" t="n">
-        <v>78519</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,40 +1466,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kroktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514276</v>
+        <v>514303</v>
       </c>
       <c r="R10" t="n">
-        <v>7001757</v>
+        <v>7001744</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1578,7 +1534,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1594,6 +1549,693 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118269045</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>514224</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7001774</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118269053</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>514249</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7001728</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118269054</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>514254</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7001725</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118269047</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>514219</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7001782</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118269056</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>514240</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7001714</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118269046</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>514221</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7001779</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118269051</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>514272</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7001780</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18942-2026 artfynd.xlsx
+++ b/artfynd/A 18942-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269044</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269049</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269052</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118473279</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269048</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269050</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269042</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269041</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269043</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269045</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269053</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269054</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269047</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269056</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269046</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2236,8 +2316,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118269051</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>